--- a/sample_apps/dst_stn_en/dst_stn_en_senario.xlsx
+++ b/sample_apps/dst_stn_en/dst_stn_en_senario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nakano\system\dialbb\dialbb-next\sample_apps\dst_stn_en\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E501D6A0-858A-4EBB-9F19-718A8736050F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BF865A-8D29-44EC-8C8E-5D4E5CE85A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3566FB2-A815-41D8-9347-99D11DD601B4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3566FB2-A815-41D8-9347-99D11DD601B4}"/>
   </bookViews>
   <sheets>
     <sheet name="scenario" sheetId="1" r:id="rId1"/>
@@ -175,9 +175,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>is_known_sandwich(#favorite-sandwich)</t>
-  </si>
-  <si>
     <t>egg-salad-sandwich</t>
   </si>
   <si>
@@ -189,10 +186,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>is_novel_sandwich(#favorite-sandwich)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>#prep</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -266,10 +259,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>topic_sandwich=#favorite-sandwich</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>confirmed=="yes"</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -284,9 +273,6 @@
     <t>confirmation_request="Sorry to ask you again, but do you often eat sadwiches?"</t>
   </si>
   <si>
-    <t>#favorite-sandwich=="egg salad sandwich"</t>
-  </si>
-  <si>
     <t>You don't like sandwich. Why you don't like them?</t>
   </si>
   <si>
@@ -302,9 +288,6 @@
     <t>I understand. $Generate a sentence to say it's time to end the talk by continuing the conversation in 50 words$ Thank you for your time.</t>
   </si>
   <si>
-    <t>Thank you {#user-name}! Let me ask you about sandwich. Do you have sandwiches very often?</t>
-  </si>
-  <si>
     <t>$Determine if the user said the reason.$</t>
   </si>
   <si>
@@ -317,7 +300,22 @@
     <t>$Did the user say he/she likes sandwiches?$</t>
   </si>
   <si>
-    <t>#user-name!=""</t>
+    <t>#user_name!=""</t>
+  </si>
+  <si>
+    <t>Thank you {#user_name}! Let me ask you about sandwich. Do you have sandwiches very often?</t>
+  </si>
+  <si>
+    <t>#favorite_sandwich=="egg salad sandwich"</t>
+  </si>
+  <si>
+    <t>topic_sandwich=#favorite_sandwich</t>
+  </si>
+  <si>
+    <t>is_known_sandwich(#favorite_sandwich)</t>
+  </si>
+  <si>
+    <t>is_novel_sandwich(#favorite_sandwich)</t>
   </si>
 </sst>
 </file>
@@ -813,10 +811,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>19</v>
@@ -830,16 +828,16 @@
         <v>19</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="5" customFormat="1">
@@ -850,7 +848,7 @@
         <v>19</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="3" customFormat="1" ht="45">
@@ -858,16 +856,16 @@
         <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>6</v>
@@ -878,13 +876,13 @@
         <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>7</v>
@@ -895,16 +893,16 @@
         <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="10" customFormat="1" ht="45">
@@ -912,16 +910,16 @@
         <v>18</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>4</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>6</v>
@@ -932,13 +930,13 @@
         <v>18</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>7</v>
@@ -949,16 +947,16 @@
         <v>18</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>34</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="2" customFormat="1">
@@ -966,14 +964,14 @@
         <v>18</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D11" s="3"/>
       <c r="F11" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
@@ -985,12 +983,12 @@
         <v>18</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="F12" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
@@ -1011,10 +1009,10 @@
         <v>9</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>10</v>
@@ -1042,13 +1040,13 @@
         <v>7</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>20</v>
@@ -1062,7 +1060,7 @@
         <v>7</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="8" customFormat="1" ht="30">
@@ -1079,13 +1077,13 @@
         <v>23</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="8" customFormat="1" ht="30">
@@ -1099,13 +1097,13 @@
         <v>12</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="8" customFormat="1" ht="30">
@@ -1119,7 +1117,7 @@
         <v>15</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>16</v>
@@ -1144,7 +1142,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>30</v>
@@ -1161,7 +1159,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>31</v>
@@ -1170,7 +1168,7 @@
         <v>17</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="9" customFormat="1" ht="60">
@@ -1181,7 +1179,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="9" customFormat="1" ht="30">
@@ -1189,10 +1187,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="5" customFormat="1" ht="45">
@@ -1200,10 +1198,10 @@
         <v>18</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="5" customFormat="1" ht="30">
@@ -1211,10 +1209,10 @@
         <v>18</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="4" customFormat="1">
@@ -1233,20 +1231,20 @@
         <v>18</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="1" customFormat="1">
@@ -1254,15 +1252,15 @@
         <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="G29" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/sample_apps/dst_stn_en/dst_stn_en_senario.xlsx
+++ b/sample_apps/dst_stn_en/dst_stn_en_senario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nakano\system\dialbb\dialbb-next\sample_apps\dst_stn_en\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BF865A-8D29-44EC-8C8E-5D4E5CE85A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F192806D-EAAD-4789-940F-9EB1E786E885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3566FB2-A815-41D8-9347-99D11DD601B4}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="74">
   <si>
     <t>conditions</t>
     <phoneticPr fontId="1"/>
@@ -44,10 +44,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>yes</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>not very often</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -148,10 +144,6 @@
   </si>
   <si>
     <t>state</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>user utterance type</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -766,501 +758,494 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9D1DC6-E066-4D71-9ECD-01107058A46B}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="6"/>
     <col min="2" max="2" width="28" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.5703125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="40.28515625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="46.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.5703125" style="6"/>
+    <col min="5" max="5" width="35.5703125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="40.28515625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="46.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.5703125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="3" customFormat="1" ht="30">
+    <row r="1" spans="1:7" s="3" customFormat="1" ht="30">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="4" customFormat="1">
+    </row>
+    <row r="2" spans="1:7" s="4" customFormat="1">
       <c r="A2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:7" s="5" customFormat="1" ht="45">
+      <c r="A3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="E3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" ht="45">
-      <c r="A3" s="5" t="s">
+    </row>
+    <row r="4" spans="1:7" s="5" customFormat="1">
+      <c r="A4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H3" s="5" t="s">
+    </row>
+    <row r="5" spans="1:7" s="3" customFormat="1" ht="45">
+      <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="3" customFormat="1" ht="30">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="3" customFormat="1" ht="30">
+      <c r="A7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="10" customFormat="1" ht="45">
+      <c r="A8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" s="5" customFormat="1">
-      <c r="A4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="D8" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="10" customFormat="1" ht="30">
+      <c r="A9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="10" customFormat="1" ht="45">
+      <c r="A10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="2" customFormat="1">
+      <c r="A11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" s="3" customFormat="1" ht="45">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="3" customFormat="1" ht="30">
-      <c r="A6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="3" customFormat="1" ht="30">
-      <c r="A7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="10" customFormat="1" ht="45">
-      <c r="A8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="10" customFormat="1" ht="30">
-      <c r="A9" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="10" customFormat="1" ht="45">
-      <c r="A10" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="2" customFormat="1">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="D11" s="3"/>
-      <c r="F11" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="2" customFormat="1">
+      <c r="E11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="2" customFormat="1">
       <c r="A12" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
-      <c r="F12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3" t="s">
+      <c r="E12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="5" customFormat="1" ht="30">
+      <c r="A13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" s="5" customFormat="1" ht="30">
-      <c r="A13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="D13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="5" customFormat="1">
+      <c r="A14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="7" customFormat="1" ht="30">
+      <c r="A15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="C15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="7" customFormat="1">
+      <c r="A16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="8" customFormat="1" ht="30">
+      <c r="A17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="5" t="s">
+      <c r="C17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="8" customFormat="1" ht="30">
+      <c r="A18" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="8" customFormat="1" ht="30">
+      <c r="A19" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="4" customFormat="1" ht="45">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="5" customFormat="1" ht="45">
+      <c r="A21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="3" customFormat="1" ht="30">
+      <c r="A22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="9" customFormat="1" ht="60">
+      <c r="A23" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="9" customFormat="1" ht="30">
+      <c r="A24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="5" customFormat="1" ht="45">
+      <c r="A25" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="5" customFormat="1">
-      <c r="A14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="7" customFormat="1" ht="30">
-      <c r="A15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" s="7" t="s">
+    </row>
+    <row r="26" spans="1:7" s="5" customFormat="1" ht="30">
+      <c r="A26" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="4" customFormat="1">
+      <c r="A27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" s="7" customFormat="1">
-      <c r="A16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" s="8" customFormat="1" ht="30">
-      <c r="A17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" s="8" customFormat="1" ht="30">
-      <c r="A18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" s="8" customFormat="1" ht="30">
-      <c r="A19" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" s="4" customFormat="1" ht="45">
-      <c r="A20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" s="5" customFormat="1" ht="45">
-      <c r="A21" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" s="3" customFormat="1" ht="30">
-      <c r="A22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" s="9" customFormat="1" ht="60">
-      <c r="A23" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" s="9" customFormat="1" ht="30">
-      <c r="A24" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" s="5" customFormat="1" ht="45">
-      <c r="A25" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" s="5" customFormat="1" ht="30">
-      <c r="A26" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" s="4" customFormat="1">
-      <c r="A27" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" s="1" customFormat="1">
+    </row>
+    <row r="28" spans="1:7" s="1" customFormat="1">
       <c r="A28" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C28" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="F28" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H28" s="1" t="s">
+    </row>
+    <row r="29" spans="1:7" s="1" customFormat="1">
+      <c r="A29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" s="1" customFormat="1">
-      <c r="A29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
-      <c r="G29" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>47</v>
+      <c r="F29" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
